--- a/关键词回答表.xlsx
+++ b/关键词回答表.xlsx
@@ -1,67 +1,150 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0d00\Desktop\qianli\ticket-pm\project-management-robot\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D820C4E-2942-4551-B673-FC8085B8CCCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关键词回答" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="关键词回答" sheetId="1" r:id="rId1"/>
+    <sheet name="使用说明" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+  <si>
+    <t>关键词自动回答表</t>
+  </si>
+  <si>
+    <t>关键词</t>
+  </si>
+  <si>
+    <t>回答</t>
+  </si>
+  <si>
+    <t>关键词示例</t>
+  </si>
+  <si>
+    <t>这是示例条目：把关键词换成要触发的词（同义词用逗号分隔放同一格），回答填命中后自动回复的内容。</t>
+  </si>
+  <si>
+    <t># 本行起为注释：# 开头的行不会被同步进机器人</t>
+  </si>
+  <si>
+    <t># 修改本表后 npm run push 自动同步并部署；npm run sync:auto-replies 只生成本地 JSON 不部署</t>
+  </si>
+  <si>
+    <t># 删除某行 = 下线该条规则；详细规则见「使用说明」工作表</t>
+  </si>
+  <si>
+    <t>填写说明</t>
+  </si>
+  <si>
+    <t>1. 每行一条规则：「关键词」列填触发词，「回答」列填命中后机器人自动回复的内容。</t>
+  </si>
+  <si>
+    <t>2. 同义词放同一格，用逗号分隔（中英文逗号、顿号、分号均可），任一命中即触发。</t>
+  </si>
+  <si>
+    <t>3. 消息文本包含关键词即触发（不分大小写）；一条消息命中多行时，回复合并为一条。</t>
+  </si>
+  <si>
+    <t>4. 「关键词」以 # 开头的行视为注释，不会同步。</t>
+  </si>
+  <si>
+    <t>5. 群范围默认所有群（审批群除外）；如需限制，配置 env 的 AUTO_REPLY_CHAT_IDS（逗号分隔 chat_id，* = 所有群）。</t>
+  </si>
+  <si>
+    <t>6. 同步方式：npm run push = 转 JSON 并随部署上线；npm run sync:auto-replies = 只生成本地 JSON。</t>
+  </si>
+  <si>
+    <t>7. 删除某行 = 下线该条；总开关 enabled 在生成的 server/src/config/autoReplies.json 里（默认开）。</t>
+  </si>
+  <si>
+    <t>8. 机器人侧无需重启：服务每次收到消息都会重读 JSON，部署完成后改动即时生效。</t>
+  </si>
+  <si>
+    <t>近看石头大</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>远看大石头</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="16"/>
+      <color rgb="FF1B2A4A"/>
       <name val="Noto Sans SC"/>
-      <color rgb="001B2A4A"/>
-      <sz val="16"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Noto Sans SC"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF37352F"/>
       <name val="Noto Sans SC"/>
-      <color rgb="0037352F"/>
-      <sz val="11"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF8C8A84"/>
       <name val="Noto Sans SC"/>
-      <color rgb="008C8A84"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B2A4A"/>
+        <fgColor rgb="FF1B2A4A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,104 +157,50 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color rgb="00E9E9E8"/>
+        <color rgb="FFE9E9E8"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -459,165 +488,134 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:C11"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1"/>
-    <row r="2" ht="32" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>关键词自动回答表</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="8" customHeight="1"/>
-    <row r="4" ht="28" customHeight="1">
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>关键词</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>回答</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>关键词示例</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>这是示例条目：把关键词换成要触发的词（同义词用逗号分隔放同一格），回答填命中后自动回复的内容。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1"/>
-    <row r="7" ht="22" customHeight="1"/>
-    <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t># 本行起为注释：# 开头的行不会被同步进机器人</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t># 修改本表后 npm run push 自动同步并部署；npm run sync:auto-replies 只生成本地 JSON 不部署</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t># 删除某行 = 下线该条规则；详细规则见「使用说明」工作表</t>
-        </is>
+    <row r="1" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:3" ht="32" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="6"/>
+    </row>
+    <row r="3" spans="2:3" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:3" ht="28" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="38" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:3" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="2:3" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:C2"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="B1:C11"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1"/>
-    <row r="2" ht="32" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>填写说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="8" customHeight="1"/>
-    <row r="4">
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>1. 每行一条规则：「关键词」列填触发词，「回答」列填命中后机器人自动回复的内容。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>2. 同义词放同一格，用逗号分隔（中英文逗号、顿号、分号均可），任一命中即触发。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>3. 消息文本包含关键词即触发（不分大小写）；一条消息命中多行时，回复合并为一条。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>4. 「关键词」以 # 开头的行视为注释，不会同步。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>5. 群范围默认所有群（审批群除外）；如需限制，配置 env 的 AUTO_REPLY_CHAT_IDS（逗号分隔 chat_id，* = 所有群）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>6. 同步方式：npm run push = 转 JSON 并随部署上线；npm run sync:auto-replies = 只生成本地 JSON。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>7. 删除某行 = 下线该条；总开关 enabled 在生成的 server/src/config/autoReplies.json 里（默认开）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>8. 机器人侧无需重启：服务每次收到消息都会重读 JSON，部署完成后改动即时生效。</t>
-        </is>
+    <row r="1" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:3" ht="32" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="6"/>
+    </row>
+    <row r="3" spans="2:3" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:3" ht="18.5" x14ac:dyDescent="0.25">
+      <c r="B4" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="18.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="18.5" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="18.5" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="18.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="18.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="18.5" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" ht="18.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:C2"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/关键词回答表.xlsx
+++ b/关键词回答表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0d00\Desktop\qianli\ticket-pm\project-management-robot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D820C4E-2942-4551-B673-FC8085B8CCCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0370FAFB-FF5F-4BCA-8C38-E77BFE9D189D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="7665" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="关键词回答" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>关键词自动回答表</t>
   </si>
@@ -79,6 +79,30 @@
   </si>
   <si>
     <t>远看大石头</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>石头果然大</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>果然大石头</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>大石头真大</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>真的大石头</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>采一块石头</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>拿来砸玉米</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -489,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:C11"/>
+  <dimension ref="B1:C14"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -543,6 +567,30 @@
       </c>
       <c r="C11" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/关键词回答表.xlsx
+++ b/关键词回答表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0d00\Desktop\qianli\ticket-pm\project-management-robot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0370FAFB-FF5F-4BCA-8C38-E77BFE9D189D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F467D5-6BCF-463A-8623-E7FE784A4DC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="7665" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28830" yWindow="12870" windowWidth="19200" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="关键词回答" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>关键词自动回答表</t>
   </si>
@@ -103,6 +103,13 @@
   </si>
   <si>
     <t>拿来砸玉米</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>🐖</t>
+  </si>
+  <si>
+    <t>杨杨文琦</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -513,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:C14"/>
+  <dimension ref="B1:C15"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -591,6 +598,14 @@
       </c>
       <c r="C14" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/关键词回答表.xlsx
+++ b/关键词回答表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0d00\Desktop\qianli\ticket-pm\project-management-robot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F467D5-6BCF-463A-8623-E7FE784A4DC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC08A56A-CB40-47CF-97BF-E221180C5958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28830" yWindow="12870" windowWidth="19200" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24840" yWindow="10785" windowWidth="19200" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="关键词回答" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>关键词自动回答表</t>
   </si>
@@ -110,6 +110,22 @@
   </si>
   <si>
     <t>杨杨文琦</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>小狗小狗</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>？</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>小狗小狗请叫叫</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>不叫</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -520,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:C15"/>
+  <dimension ref="B1:C17"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -606,6 +622,22 @@
       </c>
       <c r="C15" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/关键词回答表.xlsx
+++ b/关键词回答表.xlsx
@@ -1,197 +1,72 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0d00\Desktop\qianli\ticket-pm\project-management-robot\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC08A56A-CB40-47CF-97BF-E221180C5958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-24840" yWindow="10785" windowWidth="19200" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="关键词回答" sheetId="1" r:id="rId1"/>
-    <sheet name="使用说明" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关键词回答" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
-  <si>
-    <t>关键词自动回答表</t>
-  </si>
-  <si>
-    <t>关键词</t>
-  </si>
-  <si>
-    <t>回答</t>
-  </si>
-  <si>
-    <t>关键词示例</t>
-  </si>
-  <si>
-    <t>这是示例条目：把关键词换成要触发的词（同义词用逗号分隔放同一格），回答填命中后自动回复的内容。</t>
-  </si>
-  <si>
-    <t># 本行起为注释：# 开头的行不会被同步进机器人</t>
-  </si>
-  <si>
-    <t># 修改本表后 npm run push 自动同步并部署；npm run sync:auto-replies 只生成本地 JSON 不部署</t>
-  </si>
-  <si>
-    <t># 删除某行 = 下线该条规则；详细规则见「使用说明」工作表</t>
-  </si>
-  <si>
-    <t>填写说明</t>
-  </si>
-  <si>
-    <t>1. 每行一条规则：「关键词」列填触发词，「回答」列填命中后机器人自动回复的内容。</t>
-  </si>
-  <si>
-    <t>2. 同义词放同一格，用逗号分隔（中英文逗号、顿号、分号均可），任一命中即触发。</t>
-  </si>
-  <si>
-    <t>3. 消息文本包含关键词即触发（不分大小写）；一条消息命中多行时，回复合并为一条。</t>
-  </si>
-  <si>
-    <t>4. 「关键词」以 # 开头的行视为注释，不会同步。</t>
-  </si>
-  <si>
-    <t>5. 群范围默认所有群（审批群除外）；如需限制，配置 env 的 AUTO_REPLY_CHAT_IDS（逗号分隔 chat_id，* = 所有群）。</t>
-  </si>
-  <si>
-    <t>6. 同步方式：npm run push = 转 JSON 并随部署上线；npm run sync:auto-replies = 只生成本地 JSON。</t>
-  </si>
-  <si>
-    <t>7. 删除某行 = 下线该条；总开关 enabled 在生成的 server/src/config/autoReplies.json 里（默认开）。</t>
-  </si>
-  <si>
-    <t>8. 机器人侧无需重启：服务每次收到消息都会重读 JSON，部署完成后改动即时生效。</t>
-  </si>
-  <si>
-    <t>近看石头大</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>远看大石头</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>石头果然大</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>果然大石头</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>大石头真大</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>真的大石头</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>采一块石头</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>拿来砸玉米</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>🐖</t>
-  </si>
-  <si>
-    <t>杨杨文琦</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>小狗小狗</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>？</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>小狗小狗请叫叫</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>不叫</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Noto Sans SC"/>
+      <color rgb="001B2A4A"/>
       <sz val="16"/>
-      <color rgb="FF1B2A4A"/>
-      <name val="Noto Sans SC"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
+      <name val="Noto Sans SC"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Noto Sans SC"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF37352F"/>
       <name val="Noto Sans SC"/>
-      <family val="2"/>
-      <charset val="134"/>
+      <color rgb="008C8A84"/>
+      <sz val="9"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF8C8A84"/>
       <name val="Noto Sans SC"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <color rgb="0037352F"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1B2A4A"/>
+        <fgColor rgb="001B2A4A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F7F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -204,50 +79,107 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
-        <color rgb="FFE9E9E8"/>
+        <color rgb="00E9E9E8"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -535,182 +467,322 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:C17"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:F23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="3" width="60" customWidth="1"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:3" ht="32" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="6"/>
-    </row>
-    <row r="3" spans="2:3" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:3" ht="28" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" ht="38" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="2:3" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="2:3" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="B13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="B14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="B17" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" t="s">
-        <v>30</v>
-      </c>
-    </row>
+    <row r="1" ht="15" customHeight="1"/>
+    <row r="2" ht="32" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>关键词自动回答表</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>关键词</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>回答</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>概率1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>概率2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>概率3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t># 本行起为注释（不会同步进机器人）；正式规则请写在注释行上方</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t># 关键词 | 回答（/ 分隔多个候选）| 概率1 概率2 概率3 —— 概率按候选顺序填 0-100 整数，总和=100，留空候选自动均分剩余概率</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>关键词示例</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>这是示例条目：把关键词换成要触发的词（同义词用逗号分隔放同一格），回答填命中后自动回复的内容。</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t># 本行起为注释：# 开头的行不会被同步进机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t># 修改本表后 npm run push 自动同步并部署；npm run sync:auto-replies 只生成本地 JSON 不部署</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t># 删除某行 = 下线该条规则；详细规则见「使用说明」工作表</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>近看石头大</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>远看大石头</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>石头果然大</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>果然大石头</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>大石头真大</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>真的大石头</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>采一块石头</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>拿来砸玉米</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>🐖</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>杨杨文琦</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>小狗小狗</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>？</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>小狗小狗请叫叫</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>不叫</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t># 示例：关键词「打招呼」回答「你好/哈喽/嗨」概率1=20 概率2=30 → 你好20% 哈喽30% 嗨自动补50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B2:F2"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:C11"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="100" customWidth="1"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="115" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:3" ht="32" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="6"/>
-    </row>
-    <row r="3" spans="2:3" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:3" ht="18.5" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" ht="18.5" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" ht="18.5" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" ht="18.5" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" ht="18.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" ht="18.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" ht="18.5" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" ht="18.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="4" t="s">
-        <v>16</v>
+    <row r="1" ht="15" customHeight="1"/>
+    <row r="2" ht="32" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>填写说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>1. 一行 = 一条规则（触发槽）。「关键词」列填触发词，同义词用逗号分隔放同一格，任一命中即触发。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>2. 「回答」列支持多个候选回复，用 / 分隔（示例：远看大石头/近看小石头）。触发时按概率随机抽一条回复。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>3. 「概率1/2/3…」列依次对应回答列的第 1/2/3… 个候选（候选多于概率列时，多出的候选自动均分）。填 0-100 的整数，总和应为 100。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>4. 留空不填概率的候选：自动均分剩余概率。例：3 个候选，概率1=60 其余留空 → 60/20/20；全留空 → 均分（等概率）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>5. 填了概率但总和超过 100：按比例压缩为 100（同步时警告）。概率填 0 = 该候选永不触发。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>6. 回答内容请勿包含 / 字符（它是候选分隔符）；单条回复不写 / 即可。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>7. 「关键词」以 # 开头的行视为注释，不会同步。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>8. 触发：消息文本包含关键词即触发（不分大小写）；一条消息命中多行时，每行各抽一条合并回复。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>9. 同步：npm run push（转 JSON 并部署）；npm run sync:auto-replies（只生成本地 JSON）。机器人侧无需重启。</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:C2"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/关键词回答表.xlsx
+++ b/关键词回答表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0d00\Desktop\qianli\ticket-pm\project-management-robot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D9184FD-A559-42E2-8D55-8ABBF1975773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5DE318C-F274-4393-AAD0-524ED18F8E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24840" yWindow="10785" windowWidth="19200" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22965" yWindow="10275" windowWidth="19200" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="关键词回答" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>关键词自动回答表</t>
   </si>
@@ -93,9 +93,6 @@
   </si>
   <si>
     <t>小狗小狗请叫叫</t>
-  </si>
-  <si>
-    <t># 示例：关键词「打招呼」回答「你好/哈喽/嗨」概率1=20 概率2=30 → 你好20% 哈喽30% 嗨自动补50%</t>
   </si>
   <si>
     <t>填写说明</t>
@@ -137,6 +134,22 @@
   </si>
   <si>
     <t>杨杨文琦/张郭浩</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>大狗大狗</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>大狗叫不叫，大狗大狗请叫叫</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>？</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>不叫/叫叫叫！！！/嚼嚼嚼！！！</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -555,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:F18"/>
+  <dimension ref="B1:F19"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -676,7 +689,7 @@
         <v>21</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -687,7 +700,7 @@
         <v>22</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -698,7 +711,7 @@
         <v>23</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" s="3">
         <v>90</v>
@@ -709,8 +722,28 @@
       <c r="F17" s="3"/>
     </row>
     <row r="18" spans="2:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
-        <v>24</v>
+      <c r="B18" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="B19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19">
+        <v>70</v>
+      </c>
+      <c r="E19">
+        <v>10</v>
+      </c>
+      <c r="F19">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -734,54 +767,54 @@
     <row r="1" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:3" ht="32" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" s="7"/>
     </row>
     <row r="3" spans="2:3" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:3" ht="18.5" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="18.5" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="18.5" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="18.5" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="18.5" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="18.5" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="18.5" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="18.5" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="18.5" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/关键词回答表.xlsx
+++ b/关键词回答表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0d00\Desktop\qianli\ticket-pm\project-management-robot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5DE318C-F274-4393-AAD0-524ED18F8E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B44C99D2-F827-474E-95A7-4B1BEC71C5BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-22965" yWindow="10275" windowWidth="19200" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>关键词自动回答表</t>
   </si>
@@ -150,6 +150,14 @@
   </si>
   <si>
     <t>不叫/叫叫叫！！！/嚼嚼嚼！！！</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>是的我也喜欢你！/你喜欢我/</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>我喜欢你</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -568,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:F19"/>
+  <dimension ref="B1:F20"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -744,6 +752,20 @@
       </c>
       <c r="F19">
         <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20">
+        <v>10</v>
+      </c>
+      <c r="E20">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
